--- a/Interview_Questions/Company_Wise_Interview_Questions/Company_wise_questions.xlsx
+++ b/Interview_Questions/Company_Wise_Interview_Questions/Company_wise_questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81d526b8de137f60/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Resources-\Interview_Questions\Company_Wise_Interview_Questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7782CC75-B60F-4E7A-B1A7-689DB00682A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA1C2FC-0F7F-41D4-B590-FE561F4D762B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{2F0EB75B-C94C-418A-9324-CA797835AF84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F0EB75B-C94C-418A-9324-CA797835AF84}"/>
   </bookViews>
   <sheets>
     <sheet name="Oracle" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,13 @@
     <sheet name="IntraEdge" sheetId="10" r:id="rId9"/>
     <sheet name="EY" sheetId="12" r:id="rId10"/>
     <sheet name="HCL" sheetId="11" r:id="rId11"/>
-    <sheet name="Deloitte" sheetId="13" r:id="rId12"/>
-    <sheet name="Others" sheetId="8" r:id="rId13"/>
+    <sheet name="Tech Mahindra" sheetId="14" r:id="rId12"/>
+    <sheet name="Deloitte" sheetId="13" r:id="rId13"/>
+    <sheet name="Logixal" sheetId="18" r:id="rId14"/>
+    <sheet name="masterCard" sheetId="15" r:id="rId15"/>
+    <sheet name="Optum" sheetId="16" r:id="rId16"/>
+    <sheet name="Delhivery" sheetId="17" r:id="rId17"/>
+    <sheet name="Others" sheetId="8" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="891">
   <si>
     <t>🚀 Java Backend Developer Interview Experience 3-5 Years | Oracle</t>
   </si>
@@ -1588,13 +1593,1884 @@
   </si>
   <si>
     <t xml:space="preserve">Recently, I had the opportunity to interview with Deloitte for a Java Backend Developer role. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">TECH MAHINDRA 
+4 YOE
+L2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Java Memory Model?
+Heap vs Stack?
+What are all the memory spaces in JVM?
+Virtual thread vs normal thread, why virtual thread is faster?
+If child class is overriding a method, what all rules it needs to follow apart from same method name and arguments?
+How does CopyOnWriteArrayList work internally?
+How does ConcurrentHashMap work internally?
+Lock vs synchronized?
+ReentrantLock vs ReentrantReadWriteLock, how internally they are different?
+Why should we use finally after acquiring a lock?
+Find second highest salary employee for each department, SQL and Stream both.
+What happens internally when we start a Spring Boot application?
+How does transaction work internally in Spring?
+What is self-invocation in Spring?
+Explain Kafka architecture and important Kafka terms.
+Producer produces a message but broker dies what happens?
+What happens if one Kafka broker goes down?
+What is replication in Kafka and how does it work?
+What happens if consumer dies while processing a message?
+More partitions and less consumers what happens?
+More consumers and less partitions what happens?
+Consumer in same group vs consumer in different group?
+How is Kafka offset managed?
+How to achieve at least once guarantee without duplicate processing?
+What is KStream?
+KStream vs KTable?
+How does CI/CD pipeline work in your project?
+Count subset with sum K.</t>
+    </r>
+  </si>
+  <si>
+    <t>Until I faced these questions in an interview, I thought Java interview preparation was mostly about Core Java, Spring Boot, and coding questions.</t>
+  </si>
+  <si>
+    <t>But real-world interviews can go much deeper. 🚀</t>
+  </si>
+  <si>
+    <t>What would you do if:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Your Java application suddenly throws an </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>OutOfMemoryError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>2. CPU usage is high even though traffic is low?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. A thread is stuck in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BLOCKED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> state?</t>
+    </r>
+  </si>
+  <si>
+    <t>4. The application becomes slow after running for a few hours?</t>
+  </si>
+  <si>
+    <t>5. You are facing frequent GC pauses?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>HashMap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> creates performance issues under heavy load?</t>
+    </r>
+  </si>
+  <si>
+    <t>7. Multiple threads update shared data incorrectly?</t>
+  </si>
+  <si>
+    <t>8. An API works locally but fails in production?</t>
+  </si>
+  <si>
+    <t>9. You suspect a memory leak?</t>
+  </si>
+  <si>
+    <t>10. A service becomes randomly unresponsive?</t>
+  </si>
+  <si>
+    <t>11. You detect a deadlock?</t>
+  </si>
+  <si>
+    <t>12. Logs show inconsistent behavior across requests?</t>
+  </si>
+  <si>
+    <t>13. The application crashes without a clear error?</t>
+  </si>
+  <si>
+    <t>14. A database call is slowing down the entire service?</t>
+  </si>
+  <si>
+    <t>15. Your thread pool gets exhausted under heavy load?</t>
+  </si>
+  <si>
+    <t>16. You need to handle high concurrency safely?</t>
+  </si>
+  <si>
+    <t>17. Your system processes duplicate requests?</t>
+  </si>
+  <si>
+    <t>18. Your cache starts returning stale data?</t>
+  </si>
+  <si>
+    <t>19. Your application does not scale even after adding more instances?</t>
+  </si>
+  <si>
+    <t>20. You need to trace a request across multiple layers and services?</t>
+  </si>
+  <si>
+    <t>These are not just theoretical questions.</t>
+  </si>
+  <si>
+    <t>They test how you think as an engineer. Debugging, monitoring, concurrency, JVM internals, database performance, distributed systems, caching, scalability, and production troubleshooting are becoming equally important as writing clean code.</t>
+  </si>
+  <si>
+    <t>As developers, we should prepare beyond:</t>
+  </si>
+  <si>
+    <t>❌ What is HashMap?</t>
+  </si>
+  <si>
+    <t>❌ What is multithreading?</t>
+  </si>
+  <si>
+    <t>❌ What is Spring Boot?</t>
+  </si>
+  <si>
+    <t>And start preparing for:</t>
+  </si>
+  <si>
+    <t>✅ What happens when things fail in production?</t>
+  </si>
+  <si>
+    <t>✅ How will you debug the issue?</t>
+  </si>
+  <si>
+    <t>✅ Which tools, logs, metrics, and thread dumps will you check?</t>
+  </si>
+  <si>
+    <t>✅ How will you identify the root cause and prevent it from happening again?</t>
+  </si>
+  <si>
+    <t>The best developers are not just those who can write code.</t>
+  </si>
+  <si>
+    <t>They are the ones who can understand what happens when the code runs in the real world. 🔥</t>
+  </si>
+  <si>
+    <t>Which of these scenarios have you faced in a real project or interview? Let’s discuss in the comments. 👇</t>
+  </si>
+  <si>
+    <t>#Java #JavaDeveloper #SpringBoot #BackendDevelopment #Microservices #JVM #Concurrency #SystemDesign #SoftwareEngineering #InterviewPreparation #Debugging #TechCommunity</t>
+  </si>
+  <si>
+    <t>20. Your service’s p99 latency spiked from 80ms to 2s overnight. Walk me through your debugging process.*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Questions asked in my Mastercard First Round Interview (for Backend Developer) — and trust me, this was NOT basic 👇</t>
+  </si>
+  <si>
+    <t>If you’re preparing for product-based companies, this is your reality check.</t>
+  </si>
+  <si>
+    <t>💡 They didn’t just test theory — they went deep into real-world system design, Kafka, and clean code practices.</t>
+  </si>
+  <si>
+    <t>Here’s what was covered:</t>
+  </si>
+  <si>
+    <t>🔥 API Gateway &amp; Authentication flow</t>
+  </si>
+  <si>
+    <t>🔥 Authentication vs Authorization (with practical use cases)</t>
+  </si>
+  <si>
+    <t>🔥 Microservices architecture discussion</t>
+  </si>
+  <si>
+    <t>🔥 @Transactional → what actually rolls back? (tricky!)</t>
+  </si>
+  <si>
+    <t>🔥 SAGA pattern &amp; distributed transactions</t>
+  </si>
+  <si>
+    <t>🔥 Garbage Collector internals</t>
+  </si>
+  <si>
+    <t>🔥 Caching strategies (Redis, cache-aside)</t>
+  </si>
+  <si>
+    <t>⚡ Kafka Deep Dive:</t>
+  </si>
+  <si>
+    <t>Delivery semantics (at least once, exactly once)</t>
+  </si>
+  <si>
+    <t>Consumer failure handling</t>
+  </si>
+  <si>
+    <t>DLQs (Dead Letter Queues)</t>
+  </si>
+  <si>
+    <t>Schema Registry</t>
+  </si>
+  <si>
+    <t>Kafka vs ActiveMQ</t>
+  </si>
+  <si>
+    <t>🧠 Design &amp; Coding:</t>
+  </si>
+  <si>
+    <t>Identify problem in if-else heavy code</t>
+  </si>
+  <si>
+    <t>Apply Strategy + Factory Pattern</t>
+  </si>
+  <si>
+    <t>Serialization &amp; serialVersionUID</t>
+  </si>
+  <si>
+    <t>Making a class immutable</t>
+  </si>
+  <si>
+    <t>@ConditionalOnProperty usage</t>
+  </si>
+  <si>
+    <t>💻 Coding Question:</t>
+  </si>
+  <si>
+    <t>➡️ Find common elements in 2 lists</t>
+  </si>
+  <si>
+    <t>➡️ Optimize from O(n²) → O(n) using HashSet</t>
+  </si>
+  <si>
+    <t>⚔️ Java Concepts:</t>
+  </si>
+  <si>
+    <t>Default methods conflict in interfaces</t>
+  </si>
+  <si>
+    <t>Abstract class vs Interface (when to use what)</t>
+  </si>
+  <si>
+    <t>💬 What I realized:</t>
+  </si>
+  <si>
+    <t>👉 Interviews are no longer about “what you know”</t>
+  </si>
+  <si>
+    <t>👉 They are about “how you think in production systems”</t>
+  </si>
+  <si>
+    <t>🎯 If you’re preparing for companies like Mastercard, JPMorgan, etc:</t>
+  </si>
+  <si>
+    <t>Focus on:</t>
+  </si>
+  <si>
+    <t>✔️ Kafka + Event-driven architecture</t>
+  </si>
+  <si>
+    <t>✔️ System Design (SAGA, idempotency, retries)</t>
+  </si>
+  <si>
+    <t>✔️ Clean code &amp; design patterns</t>
+  </si>
+  <si>
+    <t>✔️ Performance optimization mindset</t>
+  </si>
+  <si>
+    <t>💥 Save this post if you’re preparing</t>
+  </si>
+  <si>
+    <t>💬 Comment “PREP” if you want a mock interview or detailed answers</t>
+  </si>
+  <si>
+    <t>#BackendDeveloper #JavaDeveloper #SystemDesign #Kafka #Microservices #InterviewPreparation #ProductBasedCompany #SoftwareEngineer #TechInterview #CodingInterview #SpringBoot #Redis #DistributedSystems #CareerGrowth #DevelopersIndia</t>
+  </si>
+  <si>
+    <t>🔥 Core Java</t>
+  </si>
+  <si>
+    <t>1. How do you sort a Map?</t>
+  </si>
+  <si>
+    <t>2. Write a Singleton class.</t>
+  </si>
+  <si>
+    <t>3. Comparable vs Comparator.</t>
+  </si>
+  <si>
+    <t>4. Features of Java 7, 8, 11, and 17.</t>
+  </si>
+  <si>
+    <t>5. What is try-with-resources?</t>
+  </si>
+  <si>
+    <t>6. What is a multi-catch statement?</t>
+  </si>
+  <si>
+    <t>7. Runnable vs Callable.</t>
+  </si>
+  <si>
+    <t>8. Types of exceptions and the Java exception hierarchy.</t>
+  </si>
+  <si>
+    <t>9. Different Design Patterns in Java.</t>
+  </si>
+  <si>
+    <t>10. OOP concepts.</t>
+  </si>
+  <si>
+    <t>11. ConcurrentHashMap internals.</t>
+  </si>
+  <si>
+    <t>12. How does Java Garbage Collection work?</t>
+  </si>
+  <si>
+    <t>💻 DSA &amp; Coding</t>
+  </si>
+  <si>
+    <t>1. Find duplicate strings in a list.</t>
+  </si>
+  <si>
+    <t>2. Check whether a string is a palindrome.</t>
+  </si>
+  <si>
+    <t>3. Combination Sum II.</t>
+  </si>
+  <si>
+    <t>4. Using Java Streams: remove odd numbers, multiply remaining numbers by a constant, and calculate the sum.</t>
+  </si>
+  <si>
+    <t>5. Find the missing integer in a consecutive array.</t>
+  </si>
+  <si>
+    <t>6. Move all zeroes to the end of an array.</t>
+  </si>
+  <si>
+    <t>7. Check whether two strings are anagrams.</t>
+  </si>
+  <si>
+    <t>8. Find the longest common prefix.</t>
+  </si>
+  <si>
+    <t>9. Longest Increasing Subsequence.</t>
+  </si>
+  <si>
+    <t>10. Best Time to Buy and Sell Stock.</t>
+  </si>
+  <si>
+    <t>11. Dijkstra’s Algorithm.</t>
+  </si>
+  <si>
+    <t>12. Coin Change Problem — minimum coins.</t>
+  </si>
+  <si>
+    <t>13. Reverse-Add Palindrome problem.</t>
+  </si>
+  <si>
+    <t>🗄️ Database &amp; SQL</t>
+  </si>
+  <si>
+    <t>1. How do you find the number of tables and their columns in a database?</t>
+  </si>
+  <si>
+    <t>2. What is the purpose of a database index?</t>
+  </si>
+  <si>
+    <t>3. How do you identify duplicate rows in SQL?</t>
+  </si>
+  <si>
+    <t>4. How would you design a schema for a ride-sharing application?</t>
+  </si>
+  <si>
+    <t>🌿 Web &amp; Frameworks</t>
+  </si>
+  <si>
+    <t>1. REST vs SOAP.</t>
+  </si>
+  <si>
+    <t>2. What is Spring?</t>
+  </si>
+  <si>
+    <t>3. Why do we use Spring?</t>
+  </si>
+  <si>
+    <t>4. Spring vs Spring Boot.</t>
+  </si>
+  <si>
+    <t>5. How does autowiring work internally?</t>
+  </si>
+  <si>
+    <t>6. What is Spring Security?</t>
+  </si>
+  <si>
+    <t>7. What is a RESTful API?</t>
+  </si>
+  <si>
+    <t>8. HTTP vs HTTPS.</t>
+  </si>
+  <si>
+    <t>🧠 System Design</t>
+  </si>
+  <si>
+    <t>1. Explain the architecture of one of your recent projects.</t>
+  </si>
+  <si>
+    <t>2. Design a fraud detection system for transactions.</t>
+  </si>
+  <si>
+    <t>3. Design the database for a ride-sharing application.</t>
+  </si>
+  <si>
+    <t>4. Design a data warehouse for an online retailer.</t>
+  </si>
+  <si>
+    <t>5. Design a news aggregator.</t>
+  </si>
+  <si>
+    <t>🖥️ Server &amp; JVM Troubleshooting</t>
+  </si>
+  <si>
+    <t>1. How do you find the reason behind a server crash?</t>
+  </si>
+  <si>
+    <t>2. How do you check server memory usage?</t>
+  </si>
+  <si>
+    <t>3. How do you debug high CPU or memory issues in a JVM application?</t>
+  </si>
+  <si>
+    <t>4. How do you capture and analyze heap dumps and thread dumps?</t>
+  </si>
+  <si>
+    <t>💡 The biggest takeaway</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>30 LPA-level opportunity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, preparation cannot be limited to:</t>
+    </r>
+  </si>
+  <si>
+    <t>❌ Core Java definitions</t>
+  </si>
+  <si>
+    <t>❌ Basic Spring Boot annotations</t>
+  </si>
+  <si>
+    <t>❌ Only LeetCode problems</t>
+  </si>
+  <si>
+    <t>You need to be comfortable with:</t>
+  </si>
+  <si>
+    <t>✅ Java internals</t>
+  </si>
+  <si>
+    <t>✅ Concurrency</t>
+  </si>
+  <si>
+    <t>✅ DSA and problem-solving</t>
+  </si>
+  <si>
+    <t>✅ SQL and database design</t>
+  </si>
+  <si>
+    <t>✅ Spring ecosystem</t>
+  </si>
+  <si>
+    <t>✅ System Design</t>
+  </si>
+  <si>
+    <t>✅ JVM troubleshooting</t>
+  </si>
+  <si>
+    <t>✅ Production debugging</t>
+  </si>
+  <si>
+    <t>The real difference at this level is not just whether you can write code.</t>
+  </si>
+  <si>
+    <t>If you’re targeting a high-paying Java Backend role at a company like JPMorganChase, don’t expect interviews to be limited to basic Java definitions.</t>
+  </si>
+  <si>
+    <t>A typical interview can cover everything from Core Java and DSA to System Design, SQL, Spring Boot, and JVM troubleshooting.</t>
+  </si>
+  <si>
+    <t>Client Interview Experience | Java Backend Developer 🚀</t>
+  </si>
+  <si>
+    <t>I recently attended a client technical interview for a Java Backend Developer role, and I’d like to share my experience to help others preparing for similar opportunities.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The interview covered </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>project discussions, Spring Boot, JPA, Hibernate, transactions, JWT, Java Streams, Microservices, RabbitMQ, and production troubleshooting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Here’s a breakdown of the questions discussed 👇</t>
+  </si>
+  <si>
+    <t>✅ Round 1 – Project &amp; Technical Discussion</t>
+  </si>
+  <si>
+    <t>1. Introduce yourself.</t>
+  </si>
+  <si>
+    <t>2. Tell me about your current project.</t>
+  </si>
+  <si>
+    <t>3. Write a REST API to fetch all employees.</t>
+  </si>
+  <si>
+    <t>4. What are JPA and Hibernate?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Write </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@OneToMany</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@ManyToOne</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> relationships using Employee and Department.</t>
+    </r>
+  </si>
+  <si>
+    <t>6. What is Fetch Type in JPA?</t>
+  </si>
+  <si>
+    <t>7. What is Cascade in JPA?</t>
+  </si>
+  <si>
+    <t>8. What is a JWT Token?</t>
+  </si>
+  <si>
+    <t>9. How do you implement JWT-based authentication?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">10. What is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Transactional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>11. What is Transaction Propagation, and what are its different types?</t>
+  </si>
+  <si>
+    <t>🔍 Scenario-Based Questions</t>
+  </si>
+  <si>
+    <t>12. Write a custom JPA query using age and salary parameters to fetch employees.</t>
+  </si>
+  <si>
+    <t>13. Within the same transaction, if I update and save a value in the database, can I retrieve the updated value in the very next line?</t>
+  </si>
+  <si>
+    <t>💻 Java Concepts &amp; Coding</t>
+  </si>
+  <si>
+    <t>14. What are Java Streams?</t>
+  </si>
+  <si>
+    <t>15. What is a Functional Interface?</t>
+  </si>
+  <si>
+    <t>16. Find the second maximum value without using Streams.</t>
+  </si>
+  <si>
+    <t>17. Find students whose marks are greater than 80 using Streams.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">18. Find the maximum marks using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sorted()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Streams.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">19. Find the maximum marks using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>max()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Streams.</t>
+    </r>
+  </si>
+  <si>
+    <t>🚀 Round 2 – Microservices &amp; Advanced Concepts</t>
+  </si>
+  <si>
+    <t>20. How do Microservices communicate with each other?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">21. Apart from </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RestTemplate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, what are other ways to communicate between Microservices?</t>
+    </r>
+  </si>
+  <si>
+    <t>22. Explain synchronous vs asynchronous communication.</t>
+  </si>
+  <si>
+    <t>23. How does RabbitMQ work?</t>
+  </si>
+  <si>
+    <t>24. What would you do if you discovered an issue in production? How would you troubleshoot it?</t>
+  </si>
+  <si>
+    <t>25. What is SLF4J, and how do you use it in your application?</t>
+  </si>
+  <si>
+    <t>26. What is a JWT Token?</t>
+  </si>
+  <si>
+    <t>27. Difference between Authentication and Authorization.</t>
+  </si>
+  <si>
+    <t>28. Which HTTP status codes represent Unauthorized and Forbidden?</t>
+  </si>
+  <si>
+    <t>29. Which occurs first in the authentication and authorization flow: Unauthorized or Forbidden?</t>
+  </si>
+  <si>
+    <t>Optum Interview Experience | Java Full Stack / Backend Developer 🚀</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I recently appeared for an interview with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Optum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and wanted to share the questions that were discussed. Hopefully, this helps anyone preparing for similar technical roles!</t>
+    </r>
+  </si>
+  <si>
+    <t>Round 1 – Technical Discussion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The round covered a mix of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>modern Java, concurrency, Spring Boot, Microservices, and React</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 Core Java &amp; Concurrency</t>
+  </si>
+  <si>
+    <t>1. What are Virtual Threads (Project Loom / Java 21), and how do they improve backend scalability?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. How do </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CompletableFuture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and Structured Concurrency enhance asynchronous REST handling?</t>
+    </r>
+  </si>
+  <si>
+    <t>3. What are Records in Java, and how do they simplify data modeling?</t>
+  </si>
+  <si>
+    <t>4. What are the key features introduced in Java 8?</t>
+  </si>
+  <si>
+    <t>5. One Java coding question.</t>
+  </si>
+  <si>
+    <t>6. Two Stream API coding questions focused on functional programming.</t>
+  </si>
+  <si>
+    <t>🔹 Spring &amp; Spring Boot</t>
+  </si>
+  <si>
+    <t>7. Explain the difference between Spring and Spring Boot in detail, with examples.</t>
+  </si>
+  <si>
+    <t>8. How do you configure and use two different databases in a single Spring Boot application?</t>
+  </si>
+  <si>
+    <t>9. Which Spring annotations have you used in your project? Explain their purpose and use cases.</t>
+  </si>
+  <si>
+    <t>10. How have you implemented caching in Spring Boot, and where does caching fit best?</t>
+  </si>
+  <si>
+    <t>🔹 Microservices</t>
+  </si>
+  <si>
+    <t>11. Which common Microservices Design Patterns have you used or are familiar with?</t>
+  </si>
+  <si>
+    <t>🔹 React / Frontend</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12. How do you use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>useEffect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> effectively?</t>
+    </r>
+  </si>
+  <si>
+    <t>The discussion also included its:</t>
+  </si>
+  <si>
+    <t>• Advantages</t>
+  </si>
+  <si>
+    <t>• Disadvantages</t>
+  </si>
+  <si>
+    <t>• Common use cases and potential pitfalls</t>
+  </si>
+  <si>
+    <t>💡 Key Takeaway</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">One thing that stood out was the focus on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>modern Java and practical implementation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>The interview wasn't limited to basic questions like:</t>
+  </si>
+  <si>
+    <t>❌ What is a REST API?</t>
+  </si>
+  <si>
+    <t>Instead, the discussion went deeper into:</t>
+  </si>
+  <si>
+    <t>✅ Virtual Threads</t>
+  </si>
+  <si>
+    <t>✅ Modern concurrency</t>
+  </si>
+  <si>
+    <t>✅ Asynchronous programming</t>
+  </si>
+  <si>
+    <t>✅ Functional programming</t>
+  </si>
+  <si>
+    <t>✅ Multi-database configuration</t>
+  </si>
+  <si>
+    <t>✅ Caching strategies</t>
+  </si>
+  <si>
+    <t>✅ Microservices patterns</t>
+  </si>
+  <si>
+    <t>✅ Modern frontend concepts</t>
+  </si>
+  <si>
+    <t>Delhivery Interview Experience | Java Full Stack Developer 🚀</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A few weeks ago, I interviewed with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Delhivery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for a Java Full Stack Developer position, and I wanted to share my experience to help others preparing for similar roles.</t>
+    </r>
+  </si>
+  <si>
+    <t>The interview process included an HR screening followed by two technical rounds.</t>
+  </si>
+  <si>
+    <t>🧩 Round 1 – Technical | Java + DSA + System Design Basics</t>
+  </si>
+  <si>
+    <t>This round was a combination of theoretical discussions and DSA problem-solving. The interviewer was friendly and allowed me to think aloud while approaching the problems.</t>
+  </si>
+  <si>
+    <t>Backend &amp; Architecture</t>
+  </si>
+  <si>
+    <t>1. Where would you choose Monolithic architecture, and where would you choose Microservices?</t>
+  </si>
+  <si>
+    <t>2. What are the drawbacks of Monolithic architecture?</t>
+  </si>
+  <si>
+    <t>3. What are the drawbacks of Microservices?</t>
+  </si>
+  <si>
+    <t>4. Difference between Monolithic and Microservices architecture.</t>
+  </si>
+  <si>
+    <t>Core Java / OOP</t>
+  </si>
+  <si>
+    <t>5. What is OOP? Explain its core principles.</t>
+  </si>
+  <si>
+    <t>Kafka</t>
+  </si>
+  <si>
+    <t>6. How does Apache Kafka work?</t>
+  </si>
+  <si>
+    <t>7. What are Consumer Groups?</t>
+  </si>
+  <si>
+    <r>
+      <t>8. What are acknowledgements (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>acks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) in Kafka?</t>
+    </r>
+  </si>
+  <si>
+    <t>Elasticsearch</t>
+  </si>
+  <si>
+    <t>9. What is Elasticsearch, and where is it used?</t>
+  </si>
+  <si>
+    <t>10. What are ACID properties?</t>
+  </si>
+  <si>
+    <t>11. Difference between SQL and NoSQL databases.</t>
+  </si>
+  <si>
+    <t>12. Where would you prefer SQL, and where would you prefer NoSQL?</t>
+  </si>
+  <si>
+    <t>Spring / Hibernate</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">13. What is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Transactional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Spring Boot, and what is its purpose?</t>
+    </r>
+  </si>
+  <si>
+    <t>14. What is Transaction Isolation?</t>
+  </si>
+  <si>
+    <t>🧠 DSA Section</t>
+  </si>
+  <si>
+    <t>The interviewer allowed me to choose a topic I was comfortable with and then asked two problems.</t>
+  </si>
+  <si>
+    <t>Problem 1 – Linked List</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You are given the head of a linked list and an integer array </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>nums</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Return the number of connected components formed by nodes whose values appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>nums</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Example:</t>
+  </si>
+  <si>
+    <t>Input:  head = [0,1,2,3]</t>
+  </si>
+  <si>
+    <t>nums = [0,1,3]</t>
+  </si>
+  <si>
+    <t>Output: 2</t>
+  </si>
+  <si>
+    <t>Problem 2 – Find Duplicate in a Read-Only Array</t>
+  </si>
+  <si>
+    <t>The array cannot be modified.</t>
+  </si>
+  <si>
+    <t>Size = N + 1</t>
+  </si>
+  <si>
+    <t>Values range from 1 to N</t>
+  </si>
+  <si>
+    <t>Find any duplicate</t>
+  </si>
+  <si>
+    <t>Time Complexity: O(N)</t>
+  </si>
+  <si>
+    <t>Space Complexity: O(1)</t>
+  </si>
+  <si>
+    <t>Input:  {10,1,2,3,5,4,9,8,5,6,4}</t>
+  </si>
+  <si>
+    <t>Output: 5</t>
+  </si>
+  <si>
+    <t>Overall, I finished this round with decent confidence.</t>
+  </si>
+  <si>
+    <t>🧩 Round 2 – Low-Level Design + Database Design</t>
+  </si>
+  <si>
+    <t>This round focused heavily on Low-Level Design and database schema thinking.</t>
+  </si>
+  <si>
+    <t>LLD Question</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Design a simplified version of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cricbuzz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that supports:</t>
+    </r>
+  </si>
+  <si>
+    <t>🏏 Live cricket scores</t>
+  </si>
+  <si>
+    <t>🏏 Match details</t>
+  </si>
+  <si>
+    <t>🏏 Player statistics</t>
+  </si>
+  <si>
+    <t>🏏 Commentary updates</t>
+  </si>
+  <si>
+    <t>The discussion included:</t>
+  </si>
+  <si>
+    <t>Class design</t>
+  </si>
+  <si>
+    <t>Entity relationships</t>
+  </si>
+  <si>
+    <t>Data flow</t>
+  </si>
+  <si>
+    <t>APIs</t>
+  </si>
+  <si>
+    <t>Storage design</t>
+  </si>
+  <si>
+    <t>Database Design</t>
+  </si>
+  <si>
+    <t>Design suitable:</t>
+  </si>
+  <si>
+    <t>Tables</t>
+  </si>
+  <si>
+    <t>Relationships</t>
+  </si>
+  <si>
+    <t>Schema structure</t>
+  </si>
+  <si>
+    <t>Query patterns</t>
+  </si>
+  <si>
+    <t>for the Cricbuzz system.</t>
+  </si>
+  <si>
+    <t>This round emphasized clarity of thought, proper class design, entity relationships, and how the system could evolve and scale as new features are added.</t>
+  </si>
+  <si>
+    <t>EY Interview Experience | Java Developer 🚀</t>
+  </si>
+  <si>
+    <t>Recently attended an interview with EY for a Java Developer role and wanted to share some of the questions and topics that were discussed.</t>
+  </si>
+  <si>
+    <t>The interview covered a wide range of areas, including Java fundamentals, Spring Boot, Microservices, AWS, DevOps, and project experience.</t>
+  </si>
+  <si>
+    <t>🔹 Introduction &amp; Project Discussion</t>
+  </si>
+  <si>
+    <t>The round started with a discussion about:</t>
+  </si>
+  <si>
+    <t>• Brief introduction about myself</t>
+  </si>
+  <si>
+    <t>• Current and previous projects</t>
+  </si>
+  <si>
+    <t>• Tech stack used</t>
+  </si>
+  <si>
+    <t>• Roles and responsibilities</t>
+  </si>
+  <si>
+    <t>• Project architecture and implementation</t>
+  </si>
+  <si>
+    <t>🔹 Spring &amp; Microservices</t>
+  </si>
+  <si>
+    <t>Some of the questions discussed were:</t>
+  </si>
+  <si>
+    <t>• Difference between Spring and Spring Boot</t>
+  </si>
+  <si>
+    <t>• How does security work in your project?</t>
+  </si>
+  <si>
+    <t>• What is Authentication and Authorization?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• What is the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@SpringBootApplication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> annotation?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• How does </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@EnableAutoConfiguration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> work internally?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• What is </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Component</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• How are beans created when we use the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Component</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> annotation?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• Difference between </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Component</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Repository</t>
+    </r>
+  </si>
+  <si>
+    <t>• Monolithic vs Microservices architecture</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• How does </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@Transactional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> work?</t>
+    </r>
+  </si>
+  <si>
+    <t>• How do microservices communicate with each other?</t>
+  </si>
+  <si>
+    <t>🔹 Core Java</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• What is the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>volatile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> keyword?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• What is the use of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>volatile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>• What are abstraction and polymorphism?</t>
+  </si>
+  <si>
+    <t>• Difference between encapsulation and abstraction</t>
+  </si>
+  <si>
+    <t>• Difference between Spring, Spring Boot, JPA, and Hibernate</t>
+  </si>
+  <si>
+    <t>🔹 AWS &amp; DevOps</t>
+  </si>
+  <si>
+    <t>• How do you deploy a service in a serverless environment?</t>
+  </si>
+  <si>
+    <t>• What is EC2, and how do you create an EC2 instance?</t>
+  </si>
+  <si>
+    <t>• How do you connect EC2 with S3?</t>
+  </si>
+  <si>
+    <t>• What is Load Balancing, and how is it configured?</t>
+  </si>
+  <si>
+    <t>• What is Auto Scaling, and how is it configured?</t>
+  </si>
+  <si>
+    <t>• How are your applications deployed in AWS?</t>
+  </si>
+  <si>
+    <t>• How do you configure a Dockerfile?</t>
+  </si>
+  <si>
+    <t>• Have you written Jenkins pipelines?</t>
+  </si>
+  <si>
+    <t>• How do you configure SonarQube?</t>
+  </si>
+  <si>
+    <t>🔹 Behavioral Questions</t>
+  </si>
+  <si>
+    <t>• What is your strength?</t>
+  </si>
+  <si>
+    <t>• What is your weakness?</t>
+  </si>
+  <si>
+    <t>🚀 Recently Attended an Interview at Logixal – Sharing My Experience</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I recently attended an interview at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Logixal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Java Developer role</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, and the overall interview process focused heavily on Java fundamentals, Spring Boot, APIs, project experience, and practical implementation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Here’s a quick breakdown of the rounds 👇</t>
+  </si>
+  <si>
+    <t>☑️ Round 1 – Technical Assessment</t>
+  </si>
+  <si>
+    <t>The assessment included:</t>
+  </si>
+  <si>
+    <t>• Java + Spring Boot MCQs</t>
+  </si>
+  <si>
+    <t>• Two coding problems:</t>
+  </si>
+  <si>
+    <t>1️⃣ An Array-based problem</t>
+  </si>
+  <si>
+    <t>2️⃣ An API-related problem</t>
+  </si>
+  <si>
+    <t>☑️ Round 2 – Technical Interview</t>
+  </si>
+  <si>
+    <t>The discussion mainly revolved around my technical skills, project experience, and backend fundamentals.</t>
+  </si>
+  <si>
+    <t>Some of the questions included:</t>
+  </si>
+  <si>
+    <t>• Introduction – technical skills, experience, and projects</t>
+  </si>
+  <si>
+    <t>• Explain your project and the features you worked on</t>
+  </si>
+  <si>
+    <t>• End-to-end API communication flow</t>
+  </si>
+  <si>
+    <t>• CRUD operations – GET, POST, PUT, DELETE</t>
+  </si>
+  <si>
+    <t>• Spring Boot annotations:</t>
+  </si>
+  <si>
+    <t>@RequestMapping</t>
+  </si>
+  <si>
+    <t>@RestController</t>
+  </si>
+  <si>
+    <t>@Autowired</t>
+  </si>
+  <si>
+    <t>• What is the entry point of a Spring Boot application?</t>
+  </si>
+  <si>
+    <t>• How have you used OOP concepts in real-world projects?</t>
+  </si>
+  <si>
+    <t>• Java Collections Framework – List, Set, and Map</t>
+  </si>
+  <si>
+    <t>• Which collections have you used in your project and where?</t>
+  </si>
+  <si>
+    <t>• What is a dependency, and where is it defined?</t>
+  </si>
+  <si>
+    <t>• What is an artifact in a dependency?</t>
+  </si>
+  <si>
+    <t>• Which Java and Spring versions are used in your project?</t>
+  </si>
+  <si>
+    <t>• How does an API request reach the correct endpoint?</t>
+  </si>
+  <si>
+    <t>• How does a React.js frontend communicate with a Spring Boot backend?</t>
+  </si>
+  <si>
+    <t>• How does Spring identify GET, POST, PUT, and DELETE requests?</t>
+  </si>
+  <si>
+    <t>• Which database have you used?</t>
+  </si>
+  <si>
+    <t>• What types of queries have you written in your project?</t>
+  </si>
+  <si>
+    <t>☑️ Round 3 – Client Interview</t>
+  </si>
+  <si>
+    <t>This round focused more on architecture, responsibilities, real-world scenarios, and problem-solving.</t>
+  </si>
+  <si>
+    <t>Questions included:</t>
+  </si>
+  <si>
+    <t>• Self-introduction</t>
+  </si>
+  <si>
+    <t>• Why is Microservices architecture preferred over Monolithic architecture?</t>
+  </si>
+  <si>
+    <t>• What is Functional Programming?</t>
+  </si>
+  <si>
+    <t>• What are your roles and responsibilities in the project?</t>
+  </si>
+  <si>
+    <t>• How does your team deploy the application to the UAT environment?</t>
+  </si>
+  <si>
+    <t>• How would you handle an urgent production defect?</t>
+  </si>
+  <si>
+    <t>• Which API have you created from scratch?</t>
+  </si>
+  <si>
+    <t>• Write a JPA query to fetch employee details with the maximum age</t>
+  </si>
+  <si>
+    <t>• Common Git commands – Pull, Push, Commit, etc.</t>
+  </si>
+  <si>
+    <t>• During migration from Java 8 to Java 17, which libraries caused compatibility issues?</t>
+  </si>
+  <si>
+    <t>• How do you call an external API from your application? Explain the theory and code flow.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1638,6 +3514,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1659,14 +3564,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1982,157 +3910,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{580CB704-B2AE-407C-90B9-028AE722AA00}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="16.5">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="16.5">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="16.5">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="16.5">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" ht="16.5">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" ht="16.5">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="16.5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" ht="16.5">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="16.5">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" ht="16.5">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="16.5">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" ht="16.5">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="16.5">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="16.5">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="16.5">
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="16.5">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="16.5">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="16.5">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="16.5">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="16.5">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="16.5">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="16.5">
       <c r="A26" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="16.5">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="16.5">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="16.5">
       <c r="A29" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="16.5">
       <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="16.5">
       <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
@@ -2144,10 +4072,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817771EF-8ACF-4BE0-B1DE-FF0F76F40ABF}">
-  <dimension ref="A2:I38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:I97"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
         <v>450</v>
       </c>
@@ -2160,7 +4088,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
         <v>451</v>
       </c>
@@ -2173,7 +4101,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
         <v>452</v>
       </c>
@@ -2186,7 +4114,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2197,7 +4125,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2208,139 +4136,349 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>477</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="23.25">
+      <c r="A42" s="8" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="18">
+      <c r="A48" s="10" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="18">
+      <c r="A58" s="10" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="18">
+      <c r="A74" s="10" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="18">
+      <c r="A82" s="10" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="18">
+      <c r="A94" s="10" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -2351,9 +4489,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF89518-6B05-4193-BC99-8D46EEAA6751}">
   <dimension ref="A2:M68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>383</v>
       </c>
@@ -2370,7 +4508,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="18.75">
       <c r="A3" s="2" t="s">
         <v>384</v>
       </c>
@@ -2387,327 +4525,327 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1">
       <c r="A62" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1">
       <c r="A63" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1">
       <c r="A64" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1">
       <c r="A65" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1">
       <c r="A66" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1">
       <c r="A67" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1">
       <c r="A68" t="s">
         <v>449</v>
       </c>
@@ -2718,11 +4856,29 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F89206-845A-44E1-8EBA-D88452A6874D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="102.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="409.5">
+      <c r="A1" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04DB512-77D9-4169-9F33-1778DBF978E6}">
   <dimension ref="A2:H51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>478</v>
       </c>
@@ -2734,7 +4890,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2744,7 +4900,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75">
       <c r="A4" s="2" t="s">
         <v>513</v>
       </c>
@@ -2756,7 +4912,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2766,7 +4922,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75">
       <c r="A6" s="2" t="s">
         <v>479</v>
       </c>
@@ -2778,12 +4934,12 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="B9" t="s">
         <v>481</v>
       </c>
@@ -2791,7 +4947,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="B10" t="s">
         <v>481</v>
       </c>
@@ -2799,7 +4955,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="B11" t="s">
         <v>481</v>
       </c>
@@ -2807,7 +4963,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="B12" t="s">
         <v>481</v>
       </c>
@@ -2815,7 +4971,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="B13" t="s">
         <v>481</v>
       </c>
@@ -2823,7 +4979,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="B14" t="s">
         <v>481</v>
       </c>
@@ -2831,12 +4987,12 @@
         <v>487</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="B17" t="s">
         <v>481</v>
       </c>
@@ -2844,12 +5000,12 @@
         <v>489</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="B20" t="s">
         <v>481</v>
       </c>
@@ -2857,22 +5013,22 @@
         <v>491</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="B26" t="s">
         <v>481</v>
       </c>
@@ -2880,7 +5036,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="B27" t="s">
         <v>481</v>
       </c>
@@ -2888,7 +5044,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="B28" t="s">
         <v>481</v>
       </c>
@@ -2896,12 +5052,12 @@
         <v>497</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="B31" t="s">
         <v>481</v>
       </c>
@@ -2909,17 +5065,17 @@
         <v>499</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="B35" t="s">
         <v>481</v>
       </c>
@@ -2927,7 +5083,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="B36" t="s">
         <v>481</v>
       </c>
@@ -2935,12 +5091,12 @@
         <v>503</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="B39" t="s">
         <v>481</v>
       </c>
@@ -2948,12 +5104,12 @@
         <v>505</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="B42" t="s">
         <v>481</v>
       </c>
@@ -2961,12 +5117,12 @@
         <v>507</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="B45" t="s">
         <v>481</v>
       </c>
@@ -2974,17 +5130,17 @@
         <v>509</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>512</v>
       </c>
@@ -2994,20 +5150,1199 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2459AAC0-F423-4947-8F95-07AC7114370E}">
-  <dimension ref="A1:M212"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D2A9D8-AD0F-43E6-B1C4-CCF91E754D60}">
+  <dimension ref="A2:A67"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>170</v>
-      </c>
+    <row r="2" spans="1:1" ht="23.25">
+      <c r="A2" s="8" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="18">
+      <c r="A8" s="10" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="18">
+      <c r="A19" s="10" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="9"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="13" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="9"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="13" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="9"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="13" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="9" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="9" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="9" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="9" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="9" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="9" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="9" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="9" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="9" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="9" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="18">
+      <c r="A51" s="10" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>890</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A8DC494-5CEB-42D7-BE2A-F384A6632D8F}">
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18.75">
+      <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" spans="1:13" ht="18.75">
+      <c r="A2" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="18.75">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A431FC97-98AD-4757-B781-09FDB2434FAC}">
+  <dimension ref="A2:A67"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="1:1" ht="23.25">
+      <c r="A2" s="8" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="18">
+      <c r="A6" s="10" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="18">
+      <c r="A10" s="10" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="9"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="9" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="9"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="9" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="9"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="9" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="9"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="9" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="9"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="9" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="9"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="9" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="18">
+      <c r="A24" s="10" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="9"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="9"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="9" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="9" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="9"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="9" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="18">
+      <c r="A34" s="10" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="9"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="9" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="18">
+      <c r="A38" s="10" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="9"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="9" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="18">
+      <c r="A48" s="10" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>737</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05D0650-F0FC-4811-A3BE-3D1F2AAABC51}">
+  <dimension ref="A2:A135"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="1:1" ht="23.25">
+      <c r="A2" s="8" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="18">
+      <c r="A10" s="10" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.75">
+      <c r="A14" s="11" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="9"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="9" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="9"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="9" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="9"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="9" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="9"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="9" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.75">
+      <c r="A24" s="11" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="9"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="9" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.75">
+      <c r="A28" s="11" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="9" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="9"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="9" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="9"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="9" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15.75">
+      <c r="A36" s="11" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="9"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.75">
+      <c r="A40" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="9"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="9" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="9" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="9"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="9" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="15.75">
+      <c r="A48" s="11" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="9"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="9" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="9"/>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="9" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="18">
+      <c r="A56" s="10" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="15.75">
+      <c r="A60" s="11" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="12" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="12" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="7"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="12" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="15.75">
+      <c r="A73" s="11" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="9"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="9" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="9"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="9" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="9"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="9" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="9"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="9" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="9"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="9" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="12" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="12" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="18">
+      <c r="A96" s="10" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="15.75">
+      <c r="A100" s="11" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="9"/>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="9" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="9"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="9" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="9"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="9" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="9"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="9" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="9"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="9" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="15.75">
+      <c r="A121" s="11" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="9"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="9" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="9"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="9" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="9"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="9" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="9"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="9" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>802</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2459AAC0-F423-4947-8F95-07AC7114370E}">
+  <dimension ref="A1:P388"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75">
+      <c r="A1" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
         <v>117</v>
       </c>
@@ -3017,162 +6352,162 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
         <v>149</v>
       </c>
@@ -3183,7 +6518,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3192,52 +6527,52 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>10</v>
       </c>
@@ -3245,57 +6580,57 @@
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="4" t="s">
         <v>171</v>
       </c>
@@ -3308,192 +6643,192 @@
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1">
       <c r="A81" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1">
       <c r="A82" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1">
       <c r="A83" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1">
       <c r="A84" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1">
       <c r="A85" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1">
       <c r="A86" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1">
       <c r="A87" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1">
       <c r="A88" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1">
       <c r="A89" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1">
       <c r="A90" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1">
       <c r="A91" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1">
       <c r="A92" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1">
       <c r="A93" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1">
       <c r="A94" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1">
       <c r="A95" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1">
       <c r="A96" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13">
       <c r="A97" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13">
       <c r="A98" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13">
       <c r="A99" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13">
       <c r="A100" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13">
       <c r="A101" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13">
       <c r="A102" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13">
       <c r="A103" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13">
       <c r="A104" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13">
       <c r="A106" s="4" t="s">
         <v>209</v>
       </c>
@@ -3510,247 +6845,247 @@
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13">
       <c r="A108" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13">
       <c r="A109" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13">
       <c r="A110" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13">
       <c r="A111" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13">
       <c r="A112" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1">
       <c r="A113" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1">
       <c r="A114" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1">
       <c r="A115" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1">
       <c r="A116" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1">
       <c r="A117" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1">
       <c r="A118" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1">
       <c r="A119" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1">
       <c r="A120" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1">
       <c r="A121" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1">
       <c r="A122" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1">
       <c r="A123" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1">
       <c r="A124" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1">
       <c r="A125" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1">
       <c r="A126" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1">
       <c r="A127" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1">
       <c r="A128" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1">
       <c r="A129" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1">
       <c r="A130" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1">
       <c r="A131" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1">
       <c r="A132" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1">
       <c r="A138" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1">
       <c r="A140" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1">
       <c r="A142" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1">
       <c r="A144" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1">
       <c r="A145" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1">
       <c r="A146" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1">
       <c r="A147" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1">
       <c r="A148" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1">
       <c r="A149" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1">
       <c r="A150" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1">
       <c r="A151" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1">
       <c r="A153" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1">
       <c r="A155" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1">
       <c r="A156" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1">
       <c r="A157" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1">
       <c r="A158" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1">
       <c r="A159" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9">
       <c r="A169" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9">
       <c r="A176" s="4" t="s">
         <v>450</v>
       </c>
@@ -3763,7 +7098,7 @@
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9">
       <c r="A177" s="4" t="s">
         <v>451</v>
       </c>
@@ -3776,7 +7111,7 @@
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9">
       <c r="A178" s="4" t="s">
         <v>452</v>
       </c>
@@ -3789,7 +7124,7 @@
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -3800,7 +7135,7 @@
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -3811,139 +7146,868 @@
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1">
       <c r="A193" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1">
       <c r="A195" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1">
       <c r="A196" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1">
       <c r="A197" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1">
       <c r="A198" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1">
       <c r="A200" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1">
       <c r="A201" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1">
       <c r="A203" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1">
       <c r="A204" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1">
       <c r="A205" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1">
       <c r="A206" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1">
       <c r="A207" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1">
       <c r="A208" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16">
       <c r="A209" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16">
       <c r="A210" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16">
       <c r="A211" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16">
       <c r="A212" t="s">
         <v>477</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="23.25">
+      <c r="A217" s="8"/>
+      <c r="B217" s="4"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+      <c r="I217" s="4"/>
+      <c r="J217" s="4"/>
+      <c r="K217" s="4"/>
+      <c r="L217" s="4"/>
+      <c r="M217" s="4"/>
+      <c r="N217" s="4"/>
+      <c r="O217" s="4"/>
+      <c r="P217" s="4"/>
+    </row>
+    <row r="218" spans="1:16">
+      <c r="A218" s="4"/>
+      <c r="B218" s="4"/>
+      <c r="C218" s="4"/>
+      <c r="D218" s="4"/>
+      <c r="E218" s="4"/>
+      <c r="F218" s="4"/>
+      <c r="G218" s="4"/>
+      <c r="H218" s="4"/>
+      <c r="I218" s="4"/>
+      <c r="J218" s="4"/>
+      <c r="K218" s="4"/>
+      <c r="L218" s="4"/>
+      <c r="M218" s="4"/>
+      <c r="N218" s="4"/>
+      <c r="O218" s="4"/>
+      <c r="P218" s="4"/>
+    </row>
+    <row r="219" spans="1:16">
+      <c r="A219" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="4"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="4"/>
+      <c r="F219" s="4"/>
+      <c r="G219" s="4"/>
+      <c r="H219" s="4"/>
+      <c r="I219" s="4"/>
+      <c r="J219" s="4"/>
+      <c r="K219" s="4"/>
+      <c r="L219" s="4"/>
+      <c r="M219" s="4"/>
+      <c r="N219" s="4"/>
+      <c r="O219" s="4"/>
+      <c r="P219" s="4"/>
+    </row>
+    <row r="220" spans="1:16">
+      <c r="A220" s="4"/>
+      <c r="B220" s="4"/>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4"/>
+      <c r="G220" s="4"/>
+      <c r="H220" s="4"/>
+      <c r="I220" s="4"/>
+      <c r="J220" s="4"/>
+      <c r="K220" s="4"/>
+      <c r="L220" s="4"/>
+      <c r="M220" s="4"/>
+      <c r="N220" s="4"/>
+      <c r="O220" s="4"/>
+      <c r="P220" s="4"/>
+    </row>
+    <row r="221" spans="1:16">
+      <c r="A221" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="4"/>
+      <c r="D221" s="4"/>
+      <c r="E221" s="4"/>
+      <c r="F221" s="4"/>
+      <c r="G221" s="4"/>
+      <c r="H221" s="4"/>
+      <c r="I221" s="4"/>
+      <c r="J221" s="4"/>
+      <c r="K221" s="4"/>
+      <c r="L221" s="4"/>
+      <c r="M221" s="4"/>
+      <c r="N221" s="4"/>
+      <c r="O221" s="4"/>
+      <c r="P221" s="4"/>
+    </row>
+    <row r="223" spans="1:16">
+      <c r="A223" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16">
+      <c r="A224" s="9"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="9"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="9" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="9"/>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="9" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="9"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="9"/>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="9" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="9"/>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="9"/>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="9" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="9"/>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="9"/>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="9" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="9"/>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="9" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="9"/>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="9" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="9"/>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="9"/>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="9" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="9"/>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="9" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="9"/>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="9"/>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="9"/>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="9"/>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="9" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="9"/>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="9"/>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B291" s="4"/>
+      <c r="C291" s="4"/>
+      <c r="D291" s="4"/>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4"/>
+      <c r="G291" s="4"/>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292" s="4"/>
+      <c r="B292" s="4"/>
+      <c r="C292" s="4"/>
+      <c r="D292" s="4"/>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4"/>
+      <c r="G292" s="4"/>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7">
+      <c r="A302">
+        <v>10</v>
+      </c>
+      <c r="B302" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7">
+      <c r="A303" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
+      <c r="A304" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" ht="23.25">
+      <c r="A316" s="8" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" ht="18">
+      <c r="A324" s="10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="9"/>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="9" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="9"/>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="9" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="9"/>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="9" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="9"/>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="9" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="9"/>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="9" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="9"/>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="9" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="9"/>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="9" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="9"/>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="9" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="9"/>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="9" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="9"/>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="9" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="9"/>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="9" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" ht="18">
+      <c r="A348" s="10" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="9"/>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="9" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="9"/>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="9" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" ht="18">
+      <c r="A354" s="10" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="9"/>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="9" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="9"/>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="9" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="9"/>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="9" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="9"/>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="9" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="9"/>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="9" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="9"/>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="9" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" ht="18">
+      <c r="A368" s="10" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="9"/>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="9" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="9"/>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="9"/>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="9" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="9"/>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="9" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="9"/>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="9" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="9"/>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="9" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="9"/>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="9" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="9"/>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="9" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="9"/>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="9" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="9"/>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="9" t="s">
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -3954,9 +8018,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF54C75B-D61E-4856-9A04-63D64DA03A6D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -3969,7 +8033,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579B3570-159F-44CB-A369-2EF647ABFAA0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3978,7 +8042,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF51EDF-38B1-4047-8376-B0A0F2109219}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3986,16 +8050,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{557E3D7E-329E-4922-A51F-C6F3E93AB690}">
-  <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="21">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="16.5">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -4009,12 +8073,8 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4027,187 +8087,187 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="16.5">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="16.5">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="16.5">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="16.5">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="16.5">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="16.5">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="16.5">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="16.5">
       <c r="A14" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16.5">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="16.5">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" ht="16.5">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" ht="16.5">
       <c r="A18" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" ht="16.5">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" ht="16.5">
       <c r="A20" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" ht="16.5">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" ht="16.5">
       <c r="A22" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" ht="16.5">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" ht="16.5">
       <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" ht="16.5">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" ht="16.5">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" ht="16.5">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" ht="16.5">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" ht="16.5">
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" ht="16.5">
       <c r="A30" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" ht="16.5">
       <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" ht="16.5">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" ht="16.5">
       <c r="A33" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" ht="16.5">
       <c r="A34" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" ht="16.5">
       <c r="A35" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" ht="16.5">
       <c r="A36" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" ht="16.5">
       <c r="A37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" ht="16.5">
       <c r="A38" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" ht="16.5">
       <c r="A39" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" ht="16.5">
       <c r="A40" s="1" t="s">
         <v>67</v>
       </c>
@@ -4220,145 +8280,145 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91AC0084-47A7-42B3-B47E-5F8E22726032}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="64.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -4371,112 +8431,112 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F8C6711-BB20-4EE5-8A07-B73966FC96DB}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="123.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>111</v>
       </c>
@@ -4488,396 +8548,783 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC13E73-C0B2-417B-8A7A-1CE204581C3B}">
-  <dimension ref="A1:C92"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D184"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="104.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="A1" s="2" t="s">
         <v>235</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1">
       <c r="A57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58">
         <v>-1</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1">
       <c r="A62" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1">
       <c r="A63" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1">
       <c r="A64" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1">
       <c r="A65" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1">
       <c r="A66" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1">
       <c r="A68" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1">
       <c r="A69" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1">
       <c r="A70" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1">
       <c r="A71" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1">
       <c r="A72" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1">
       <c r="A73" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1">
       <c r="A75" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1">
       <c r="A76" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1">
       <c r="A77" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1">
       <c r="A78" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1">
       <c r="A79" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1">
       <c r="A80" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>307</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+    </row>
+    <row r="99" spans="1:4" ht="18">
+      <c r="A99" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="9"/>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="9" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="9" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="9" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="9" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="9" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="9" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="9" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="9" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="9" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="9" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="18">
+      <c r="A114" s="10" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="9"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="9" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="9" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="9" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="9" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="9" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="9" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="9" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="9" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="9" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="9" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="9" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="9" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="18">
+      <c r="A130" s="10" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="9"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="9" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="9" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="9" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="18">
+      <c r="A137" s="10" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="9"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="9" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="9" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="9" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="9" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="9" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="9" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="18">
+      <c r="A148" s="10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="9"/>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="9" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="9" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="9" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="9" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="9" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="18">
+      <c r="A156" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="9"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="9" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="9" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="9" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="9" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="18">
+      <c r="A165" s="10" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -4888,12 +9335,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBCBB34-D242-4CF5-AEE9-97E137906727}">
   <dimension ref="A2:D63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>308</v>
       </c>
@@ -4901,263 +9348,263 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="18.75">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1">
       <c r="A63" t="s">
         <v>359</v>
       </c>
